--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,7 +872,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/identifier/app-sample-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/identifier/app-sample-code</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1024,7 +1024,7 @@
     <t>Specimen.identifier:remoteSampleCode.system</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/identifier/remote-sample-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/identifier/remote-sample-code</t>
   </si>
   <si>
     <t>Specimen.identifier:remoteSampleCode.value</t>
@@ -1093,7 +1093,7 @@
     <t>Specimen.identifier:sampleCode.system</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/identifier/sample-id</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/identifier/sample-code</t>
   </si>
   <si>
     <t>Specimen.identifier:sampleCode.value</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-viral-load-specimen.xlsx
+++ b/branches/master/StructureDefinition-viral-load-specimen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
